--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N69_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N69_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.43300760250098</v>
+        <v>6.570363735406409</v>
       </c>
       <c r="D2" t="n">
-        <v>15.34428576108966</v>
+        <v>2.493446436177071</v>
       </c>
       <c r="E2" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F2" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.43479648738877</v>
+        <v>8.520654429200675</v>
       </c>
       <c r="D3" t="n">
-        <v>33.41044491273855</v>
+        <v>5.429197298320015</v>
       </c>
       <c r="E3" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F3" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.45061510810754</v>
+        <v>4.785724955067475</v>
       </c>
       <c r="D4" t="n">
-        <v>10.30885878477556</v>
+        <v>1.675189552526029</v>
       </c>
       <c r="E4" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F4" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>65.51488233910226</v>
+        <v>10.64616838010412</v>
       </c>
       <c r="D5" t="n">
-        <v>51.81205741310526</v>
+        <v>8.419459329629605</v>
       </c>
       <c r="E5" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F5" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.66813984477999</v>
+        <v>3.846072724776748</v>
       </c>
       <c r="D6" t="n">
-        <v>8.852033782509277</v>
+        <v>1.438455489657758</v>
       </c>
       <c r="E6" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F6" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.79907376940954</v>
+        <v>6.46734948752905</v>
       </c>
       <c r="D7" t="n">
-        <v>27.07013243117337</v>
+        <v>4.398896520065673</v>
       </c>
       <c r="E7" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F7" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.86166301457006</v>
+        <v>7.615020239867635</v>
       </c>
       <c r="D8" t="n">
-        <v>45.23919837314145</v>
+        <v>7.351369735635486</v>
       </c>
       <c r="E8" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F8" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>18.34903558327053</v>
+        <v>2.981718282281461</v>
       </c>
       <c r="D9" t="n">
-        <v>35.53174080441087</v>
+        <v>5.773907880716766</v>
       </c>
       <c r="E9" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F9" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>48.8722694496914</v>
+        <v>7.941743785574853</v>
       </c>
       <c r="D10" t="n">
-        <v>28.5</v>
+        <v>4.631250000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F10" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.36387842928816</v>
+        <v>5.746630244759327</v>
       </c>
       <c r="D11" t="n">
-        <v>47.49602621841052</v>
+        <v>7.718104260491709</v>
       </c>
       <c r="E11" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F11" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1612159909709</v>
+        <v>5.388697598532771</v>
       </c>
       <c r="D12" t="n">
-        <v>37.92556385024761</v>
+        <v>6.162904125665237</v>
       </c>
       <c r="E12" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F12" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.95419361701613</v>
+        <v>4.217556462765121</v>
       </c>
       <c r="D13" t="n">
-        <v>37.32332655061546</v>
+        <v>6.065040564475011</v>
       </c>
       <c r="E13" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F13" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>33.53996981114532</v>
+        <v>5.450245094311114</v>
       </c>
       <c r="D14" t="n">
-        <v>15.44955595517006</v>
+        <v>2.510552842715134</v>
       </c>
       <c r="E14" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F14" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>62.90735126255736</v>
+        <v>10.22244458016557</v>
       </c>
       <c r="D15" t="n">
-        <v>5.830951894845301</v>
+        <v>0.9475296829123614</v>
       </c>
       <c r="E15" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F15" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>35.6154904863057</v>
+        <v>5.787517204024677</v>
       </c>
       <c r="D16" t="n">
-        <v>2.534447324237758</v>
+        <v>0.4118476901886357</v>
       </c>
       <c r="E16" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F16" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>40.17702290821364</v>
+        <v>6.528766222584717</v>
       </c>
       <c r="D17" t="n">
-        <v>12.12479193348817</v>
+        <v>1.970278689191827</v>
       </c>
       <c r="E17" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F17" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>42.93446252268129</v>
+        <v>6.976850159935709</v>
       </c>
       <c r="D18" t="n">
-        <v>14.78317007697247</v>
+        <v>2.402265137508027</v>
       </c>
       <c r="E18" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F18" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>34.95635174092388</v>
+        <v>5.68040715790013</v>
       </c>
       <c r="D19" t="n">
-        <v>19.56953493407946</v>
+        <v>3.180049426787913</v>
       </c>
       <c r="E19" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F19" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>29.9760069842667</v>
+        <v>4.871101134943339</v>
       </c>
       <c r="D20" t="n">
-        <v>11.79001693880149</v>
+        <v>1.915877752555242</v>
       </c>
       <c r="E20" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F20" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>49.55867181711287</v>
+        <v>8.053284170280842</v>
       </c>
       <c r="D21" t="n">
-        <v>4.522482606160269</v>
+        <v>0.7349034235010437</v>
       </c>
       <c r="E21" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F21" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>21.18224775415823</v>
+        <v>3.442115260050712</v>
       </c>
       <c r="D22" t="n">
-        <v>6.395525801344739</v>
+        <v>1.03927294271852</v>
       </c>
       <c r="E22" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F22" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>12.37941840313995</v>
+        <v>2.011655490510242</v>
       </c>
       <c r="D23" t="n">
-        <v>5.998288710592496</v>
+        <v>0.9747219154712807</v>
       </c>
       <c r="E23" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F23" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>3.383183993983531</v>
+        <v>0.5497673990223237</v>
       </c>
       <c r="D24" t="n">
-        <v>12.86383403056962</v>
+        <v>2.090373029967563</v>
       </c>
       <c r="E24" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F24" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>29.36044358930507</v>
+        <v>4.771072083262075</v>
       </c>
       <c r="D25" t="n">
-        <v>20.8577882628875</v>
+        <v>3.389390592719219</v>
       </c>
       <c r="E25" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F25" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>17.19381011857936</v>
+        <v>2.793994144269146</v>
       </c>
       <c r="D26" t="n">
-        <v>18.06239186818844</v>
+        <v>2.935138678580622</v>
       </c>
       <c r="E26" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F26" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>27.22931376514497</v>
+        <v>4.424763486836057</v>
       </c>
       <c r="D27" t="n">
-        <v>25.70992026436488</v>
+        <v>4.177862042959293</v>
       </c>
       <c r="E27" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F27" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>45.78891819159716</v>
+        <v>7.440699206134539</v>
       </c>
       <c r="D28" t="n">
-        <v>50.75283091814632</v>
+        <v>8.247335024198776</v>
       </c>
       <c r="E28" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F28" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>23.61954417180396</v>
+        <v>3.838175927918144</v>
       </c>
       <c r="D29" t="n">
-        <v>12.35902935411854</v>
+        <v>2.008342270044263</v>
       </c>
       <c r="E29" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F29" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>50.73491048440724</v>
+        <v>8.244422953716178</v>
       </c>
       <c r="D30" t="n">
-        <v>63.72931939327464</v>
+        <v>10.35601440140713</v>
       </c>
       <c r="E30" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F30" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>32.20832753382945</v>
+        <v>5.233853224247285</v>
       </c>
       <c r="D31" t="n">
-        <v>15.71320408787669</v>
+        <v>2.553395664279963</v>
       </c>
       <c r="E31" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F31" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>51.33298884227972</v>
+        <v>8.341610686870455</v>
       </c>
       <c r="D32" t="n">
-        <v>55.32368724845715</v>
+        <v>8.990099177874288</v>
       </c>
       <c r="E32" t="n">
-        <v>14.04932201375081</v>
+        <v>2.283014827234506</v>
       </c>
       <c r="F32" t="n">
-        <v>16.85997157487725</v>
+        <v>2.739745380917554</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
